--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260916.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260916.xlsx
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,366,384</t>
+          <t>2,573,703</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2,573,703</t>
+          <t>4,414,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,414,578</t>
+          <t>1,366,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,174,076</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>1,174,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>769,000</t>
+          <t>4,915,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>317,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>4,915,956</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>317,000</t>
+          <t>493,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>797,000</t>
+          <t>288,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>493,000</t>
+          <t>769,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>994,121</t>
+          <t>1,742,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,742,000</t>
+          <t>994,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>674,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>674,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
